--- a/docs/Bfinz-API-Documentation.xlsx
+++ b/docs/Bfinz-API-Documentation.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp\htdocs\Bfinz-Adminpanel\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4273FE1C-398E-419F-A312-DBAB357DAD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="OTP Login API" sheetId="1" r:id="rId4"/>
+    <sheet name="OTP Login API" sheetId="1" r:id="rId1"/>
+    <sheet name="Master &amp; Config API" sheetId="2" r:id="rId2"/>
+    <sheet name="Market Data API" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="113">
   <si>
     <t>Framework
 API Type
@@ -110,28 +117,10 @@
 }</t>
   </si>
   <si>
-    <t>{
-  "status": false,
-  "message": "Too many OTP requests. Please wait 10 minutes and try again."
-}
-(HTTP 429)</t>
-  </si>
-  <si>
     <t>Verify OTP (Login)</t>
   </si>
   <si>
     <t>http://localhost/api/v1/auth/verify-otp</t>
-  </si>
-  <si>
-    <t>{
-  "mobile": "9876543210",
-  "otp": "1234",
-  "name": "John Doe",
-  "device_name": "iphone-15-pro",
-  "platform": "ios",
-  "fcm_token": "sample-fcm-token"
-}
-(name, device_name, platform, fcm_token are optional)</t>
   </si>
   <si>
     <t>{
@@ -148,13 +137,6 @@
   "message": "Invalid OTP. Please try again."
 }
 (HTTP 422)</t>
-  </si>
-  <si>
-    <t>{
-  "status": false,
-  "message": "OTP has expired. Please request a new one."
-}
-(HTTP 422 - also: "No OTP found...", "Too many failed attempts..." HTTP 429)</t>
   </si>
   <si>
     <t>Get Profile</t>
@@ -272,45 +254,378 @@
 }
 (revokes every Sanctum token this user holds)</t>
   </si>
+  <si>
+    <t>{
+  "status": false,
+  "message": "Please wait 30 seconds before requesting another OTP."
+}
+(HTTP 429 - resend cooldown)
+OR
+{
+  "status": false,
+  "message": "Too many OTP requests for this number. Please try again in an hour."
+}
+(HTTP 429 - max 5 sends/hour, enforced per mobile AND per IP)</t>
+  </si>
+  <si>
+    <t>{
+  "mobile": "9876543210",
+  "otp": "123456",
+  "name": "John Doe",
+  "device_name": "iphone-15-pro",
+  "platform": "ios",
+  "fcm_token": "sample-fcm-token",
+  "app_version": "1.2.3"
+}
+(name, device_name, platform, fcm_token, app_version are optional)</t>
+  </si>
+  <si>
+    <t>{
+  "status": false,
+  "message": "OTP has expired. Please request a new one."
+}
+(HTTP 422 - OTP now expires after 5 minutes, not 10. Also: "No OTP found..." HTTP 422, "Too many failed attempts..." HTTP 429 after 5 wrong tries)</t>
+  </si>
+  <si>
+    <t>Resend OTP</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/auth/resend-otp</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": null,
+  "message": "OTP resent successfully."
+}</t>
+  </si>
+  <si>
+    <t>{
+  "status": false,
+  "message": "Validation failed."
+}
+(HTTP 422)</t>
+  </si>
+  <si>
+    <t>Same rate-limit responses as Send OTP (429 - cooldown / hourly cap)</t>
+  </si>
+  <si>
+    <t>Delete Profile (Account Deletion)</t>
+  </si>
+  <si>
+    <t>DELETE</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": null,
+  "message": "Account deleted."
+}
+(soft-deletes and anonymises the account: mobile/name/email cleared, all tokens and FCM devices revoked)</t>
+  </si>
+  <si>
+    <t>Register Device</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/auth/devices</t>
+  </si>
+  <si>
+    <t>{
+  "fcm_token": "sample-fcm-token",
+  "device_name": "iphone-15-pro",
+  "platform": "ios",
+  "app_version": "1.2.3"
+}
+(device_name, platform, app_version optional)
+Header: Authorization: Bearer {token}</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": null,
+  "message": "Device registered."
+}
+(upserts by fcm_token - re-registering the same token updates it)</t>
+  </si>
+  <si>
+    <t>Laravel 12
+REST full API
+GET (read-only, cached)
+SQLite (dev) / MySQL (prod)
+http://localhost/api/v1
+See OTP Login API sheet for the Postman collection</t>
+  </si>
+  <si>
+    <t>List States</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/master/states</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": [ { "id": 1, "name": "Andhra Pradesh", "code": "AP" }, "..." ]
+}
+(cached 24h)</t>
+  </si>
+  <si>
+    <t>List Cities</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/master/cities?state_id=</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": [ { "id": 1, "state_id": 1, "name": "Mumbai", "lat": 19.076, "lng": 72.8777 } ]
+}
+(state_id optional; cached 24h)</t>
+  </si>
+  <si>
+    <t>{
+  "status": false,
+  "message": "Validation failed."
+}
+(HTTP 422 - unknown state_id)</t>
+  </si>
+  <si>
+    <t>List Banks</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/master/banks?category=</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": [ { "id": 1, "name": "State Bank of India", "short_name": "SBI", "category": "public", "rating": 4.2 } ]
+}
+(category: public|private|sfb|nbfc|foreign|cooperative, optional; only is_active banks; cached 6h)</t>
+  </si>
+  <si>
+    <t>{
+  "status": false,
+  "message": "Validation failed."
+}
+(HTTP 422 - unknown category)</t>
+  </si>
+  <si>
+    <t>App Config</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/app/config</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": { "min_version": "1.0.0", "force_update": false, "quick_actions": [], "banners": [] }
+}
+(admin-editable via Settings; cached 10 min)</t>
+  </si>
+  <si>
+    <t>Gold/Silver Live Rate</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/metals/{metal}/live?city_id=</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": [ { "purity": "24k", "per_gram": 7000.00, "per_8g": 56000.00, "per_10g": 70000.00, "change": 25.00, "change_pct": 0.36 } ],
+  "updated_at": "2026-09-23T09:00:00+05:30",
+  "stale": false
+}
+({metal} = gold|silver. Falls back to the national rate if the city has no premium configured yet.</t>
+  </si>
+  <si>
+    <t>{
+  "status": false,
+  "message": "Unknown metal."
+}
+(HTTP 404)</t>
+  </si>
+  <si>
+    <t>Gold/Silver Details</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/metals/{metal}/details?city_id=</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": { "today": {"..."}, "seven_day_high": { "rate": 7050.00, "date": "2026-09-20" }, "seven_day_low": { "rate": 6900.00, "date": "2026-09-18" } },
+  "updated_at": "...",
+  "stale": false
+}</t>
+  </si>
+  <si>
+    <t>{
+  "status": false,
+  "message": "No rates available yet for this metal."
+}
+(HTTP 404)</t>
+  </si>
+  <si>
+    <t>Gold/Silver Trend</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/metals/{metal}/trend?purity=&amp;range=</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": [ { "date": "2026-09-16", "rate": 6950.00 }, "..." ]
+}
+(range: 7d|1m|6m|1y, default 1m; purity optional, defaults to the metal's primary purity)</t>
+  </si>
+  <si>
+    <t>Gold/Silver Cities</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/metals/{metal}/cities?state_id=</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": [ { "city_id": 5, "name": "Mumbai", "per_gram": 7010.00 } ]
+}
+(only cities with a configured premium/rate are listed)</t>
+  </si>
+  <si>
+    <t>Forex Rates</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/forex/rates?group=</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": [ { "code": "USD", "rate": 83.50, "change": 0.10, "change_pct": 0.12, "updated_at": "..." } ],
+  "updated_at": "...",
+  "stale": false
+}
+(group: all|popular|asia|middle_east|europe|americas|other, default all)</t>
+  </si>
+  <si>
+    <t>Forex Detail + History</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/forex/{code}?range=</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": { "current": { "code": "USD", "rate": 83.50 }, "history": [ { "date": "2026-09-16", "rate": 83.10 } ] },
+  "updated_at": "...",
+  "stale": false
+}
+({code} = 3-letter currency code; range: 7d|1m|6m|1y, default 1m)</t>
+  </si>
+  <si>
+    <t>{
+  "status": false,
+  "message": "No rate available for this currency."
+}
+(HTTP 404)</t>
+  </si>
+  <si>
+    <t>Forex Movers</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/forex/movers</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": { "top_gainers": [ "..." ], "top_losers": [ "..." ] }
+}
+(top 5 each, by change_pct across active currencies)</t>
+  </si>
+  <si>
+    <t>Forex Currencies</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/forex/currencies</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": [ { "code": "USD", "name": "US Dollar", "country": "United States", "group": "popular" } ]
+}
+(active currencies only; cached 24h)</t>
+  </si>
+  <si>
+    <t>Fuel Prices</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/fuel/prices?fuel=&amp;state_id=&amp;city_id=</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": [ { "fuel": "petrol", "city_id": 5, "city": "Mumbai", "price": 105.00, "change": 0.20, "updated_at": "2026-09-23" } ]
+}
+(fuel required: petrol|diesel|cng; one row per city, latest price)</t>
+  </si>
+  <si>
+    <t>{
+  "status": false,
+  "message": "Validation failed."
+}
+(HTTP 422 - fuel is required)</t>
+  </si>
+  <si>
+    <t>Fuel Trend</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/fuel/trend?fuel=&amp;city_id=&amp;range=</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": [ { "date": "2026-09-16", "rate": 104.50 } ]
+}
+(fuel and city_id required; range: 7d|1m|6m|1y, default 1m)</t>
+  </si>
+  <si>
+    <t>Fuel Cities</t>
+  </si>
+  <si>
+    <t>http://localhost/api/v1/fuel/cities?fuel=&amp;state_id=</t>
+  </si>
+  <si>
+    <t>{
+  "status": true,
+  "data": [ { "city_id": 5, "name": "Mumbai", "price": 105.00 } ]
+}
+(fuel required; only cities with a price entered are listed)</t>
+  </si>
+  <si>
+    <t>Note: Fuel prices have no automated sync yet (source TBD - see docs/PROGRESS.md open question). Gold/Silver/Forex are synced by scheduled jobs; the app never calls a provider directly.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFC00000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -369,32 +684,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -684,272 +1011,875 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="true" style="0"/>
-    <col min="2" max="2" width="24" customWidth="true" style="0"/>
-    <col min="3" max="3" width="10" customWidth="true" style="0"/>
-    <col min="4" max="4" width="34" customWidth="true" style="0"/>
-    <col min="5" max="5" width="34" customWidth="true" style="0"/>
-    <col min="6" max="6" width="40" customWidth="true" style="0"/>
-    <col min="7" max="7" width="34" customWidth="true" style="0"/>
-    <col min="8" max="8" width="34" customWidth="true" style="0"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="8" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" customHeight="1" ht="110">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="110.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="8" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" customHeight="1" ht="20">
-      <c r="A2" s="3" t="s">
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+    </row>
+    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" customHeight="1" ht="105">
-      <c r="A3" s="5">
+    <row r="3" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" customHeight="1" ht="105">
-      <c r="A4" s="5">
+      <c r="G3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" customHeight="1" ht="105">
-      <c r="A5" s="5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="6" t="s">
+      <c r="D7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s">
         <v>26</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="E12" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" customHeight="1" ht="105">
-      <c r="A6" s="5">
-        <v>4</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" customHeight="1" ht="105">
-      <c r="A7" s="5">
-        <v>5</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="F12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" customHeight="1" ht="105">
-      <c r="A8" s="5">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" customHeight="1" ht="105">
-      <c r="A9" s="5">
-        <v>7</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" customHeight="1" ht="105">
-      <c r="A10" s="5">
-        <v>8</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>13</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells>
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:H1"/>
   </mergeCells>
-  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8E31F57-0493-4948-9E85-5961103968F8}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="8" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="110.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+    </row>
+    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC6F4736-6B1E-4E43-9343-529D966C31C8}">
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="40" customWidth="1"/>
+    <col min="7" max="8" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="110.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+    </row>
+    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>110</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="B14:H14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>